--- a/2026/BRIN 3219/Julio/BRIN3219-EXPENSAS-Julio.xlsx
+++ b/2026/BRIN 3219/Julio/BRIN3219-EXPENSAS-Julio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9656C2-2811-450B-B0D9-86BD979C8EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC82FFF9-BA1E-4B33-80F4-28E922007374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -19,19 +19,22 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$O$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$92</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="157">
   <si>
     <t>U.F.</t>
   </si>
@@ -474,9 +477,6 @@
     <t>INGRESO</t>
   </si>
   <si>
-    <t>Nico Plagas - Desratizacion</t>
-  </si>
-  <si>
     <t>Ingreso por alquiler Piso 6 UF 24 y Expensas</t>
   </si>
   <si>
@@ -486,27 +486,12 @@
     <t>Extraordinarias</t>
   </si>
   <si>
-    <t>subidos en m4rz0</t>
-  </si>
-  <si>
     <t>Reemplazo por vacaciones</t>
   </si>
   <si>
     <t>Seguro - Reemplazo</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>MAM - Sistema de camaras</t>
-  </si>
-  <si>
-    <t>Honorarios Sr. Ezequiel Sarro - Abogado</t>
-  </si>
-  <si>
-    <t>Pago de convenio sindicato (abogado Maximiliano Nicolas Oliver Abogado del Sindicato para la apertura del pago de deuda de la cual estamos intimados)</t>
-  </si>
-  <si>
     <t>VTO: 17/8</t>
   </si>
   <si>
@@ -522,13 +507,16 @@
     <t>Cuota 4 de 5 - Limpieza de columnas, cocina y baño de todas las unidades funcionales - Cuello Natalia</t>
   </si>
   <si>
-    <t>Facundo heredia -</t>
-  </si>
-  <si>
     <t>Doartero Julio - Reparacion flotante de entrada de agua</t>
   </si>
   <si>
     <t>Doartero Julio - Visita electrica</t>
+  </si>
+  <si>
+    <t>Acuerdo de deuda - Sindicatos</t>
+  </si>
+  <si>
+    <t>subidos en jul10</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1332,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1642,9 +1630,93 @@
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1663,12 +1735,6 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1690,84 +1756,6 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1803,16 +1791,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2260,17 +2238,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K98"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2337,7 +2315,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2348,10 +2326,10 @@
         <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2380,14 +2358,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="218"/>
-      <c r="B12" s="187"/>
-      <c r="C12" s="187"/>
-      <c r="D12" s="187"/>
-      <c r="E12" s="187"/>
-      <c r="F12" s="187"/>
-      <c r="G12" s="187"/>
-      <c r="H12" s="219"/>
+      <c r="A12" s="212"/>
+      <c r="B12" s="213"/>
+      <c r="C12" s="213"/>
+      <c r="D12" s="213"/>
+      <c r="E12" s="213"/>
+      <c r="F12" s="213"/>
+      <c r="G12" s="213"/>
+      <c r="H12" s="214"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2399,17 +2377,17 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="220" t="s">
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="215" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="220"/>
-      <c r="C14" s="220"/>
-      <c r="D14" s="220"/>
-      <c r="E14" s="220"/>
-      <c r="F14" s="220"/>
-      <c r="G14" s="220"/>
-      <c r="H14" s="220"/>
+      <c r="B14" s="215"/>
+      <c r="C14" s="215"/>
+      <c r="D14" s="215"/>
+      <c r="E14" s="215"/>
+      <c r="F14" s="215"/>
+      <c r="G14" s="215"/>
+      <c r="H14" s="215"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="172" t="s">
@@ -2422,7 +2400,7 @@
       <c r="F15" s="137"/>
       <c r="G15" s="137"/>
       <c r="H15" s="73">
-        <v>619789.12</v>
+        <v>400043.91</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2436,7 +2414,7 @@
       <c r="F16" s="137"/>
       <c r="G16" s="137"/>
       <c r="H16" s="73">
-        <v>-97616.78</v>
+        <v>-63006.91</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -2451,7 +2429,7 @@
       <c r="F17" s="137"/>
       <c r="G17" s="137"/>
       <c r="H17" s="73">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -2467,25 +2445,25 @@
       <c r="G18" s="137"/>
       <c r="H18" s="69">
         <f>SUM(H15:H17)</f>
-        <v>522172.99999999994</v>
+        <v>337037</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="214" t="s">
+      <c r="A19" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="214"/>
-      <c r="C19" s="214"/>
-      <c r="D19" s="214"/>
-      <c r="E19" s="214"/>
-      <c r="F19" s="214"/>
-      <c r="G19" s="214"/>
-      <c r="H19" s="214"/>
+      <c r="B19" s="211"/>
+      <c r="C19" s="211"/>
+      <c r="D19" s="211"/>
+      <c r="E19" s="211"/>
+      <c r="F19" s="211"/>
+      <c r="G19" s="211"/>
+      <c r="H19" s="211"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="172" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B20" s="137"/>
       <c r="C20" s="137"/>
@@ -2499,7 +2477,7 @@
     </row>
     <row r="21" spans="1:9" hidden="1">
       <c r="A21" s="172" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B21" s="137"/>
       <c r="C21" s="137"/>
@@ -2527,16 +2505,16 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="213" t="s">
+      <c r="A23" s="210" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="213"/>
-      <c r="C23" s="213"/>
-      <c r="D23" s="213"/>
-      <c r="E23" s="213"/>
-      <c r="F23" s="213"/>
-      <c r="G23" s="213"/>
-      <c r="H23" s="213"/>
+      <c r="B23" s="210"/>
+      <c r="C23" s="210"/>
+      <c r="D23" s="210"/>
+      <c r="E23" s="210"/>
+      <c r="F23" s="210"/>
+      <c r="G23" s="210"/>
+      <c r="H23" s="210"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="137" t="s">
@@ -2610,7 +2588,7 @@
       <c r="E29" s="137"/>
       <c r="F29" s="137"/>
       <c r="G29" s="137"/>
-      <c r="H29" s="241">
+      <c r="H29" s="73">
         <f>96723.22+60583.82</f>
         <v>157307.04</v>
       </c>
@@ -2656,7 +2634,7 @@
       <c r="G32" s="206"/>
       <c r="H32" s="206"/>
     </row>
-    <row r="33" spans="1:9" ht="14.25" customHeight="1">
+    <row r="33" spans="1:11" ht="14.25" customHeight="1">
       <c r="A33" s="137" t="s">
         <v>136</v>
       </c>
@@ -2666,11 +2644,11 @@
       <c r="E33" s="137"/>
       <c r="F33" s="137"/>
       <c r="G33" s="137"/>
-      <c r="H33" s="241">
+      <c r="H33" s="73">
         <v>283260.5</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:11">
       <c r="A34" s="174" t="s">
         <v>98</v>
       </c>
@@ -2680,11 +2658,11 @@
       <c r="E34" s="137"/>
       <c r="F34" s="137"/>
       <c r="G34" s="137"/>
-      <c r="H34" s="241">
+      <c r="H34" s="73">
         <v>83971.55</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:11">
       <c r="A35" s="137" t="s">
         <v>73</v>
       </c>
@@ -2699,19 +2677,19 @@
         <v>367232.05</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="220" t="s">
+    <row r="36" spans="1:11">
+      <c r="A36" s="215" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="220"/>
-      <c r="C36" s="220"/>
-      <c r="D36" s="220"/>
-      <c r="E36" s="220"/>
-      <c r="F36" s="220"/>
-      <c r="G36" s="220"/>
-      <c r="H36" s="220"/>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="B36" s="215"/>
+      <c r="C36" s="215"/>
+      <c r="D36" s="215"/>
+      <c r="E36" s="215"/>
+      <c r="F36" s="215"/>
+      <c r="G36" s="215"/>
+      <c r="H36" s="215"/>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="80" t="s">
         <v>68</v>
       </c>
@@ -2721,13 +2699,13 @@
       <c r="E37" s="137"/>
       <c r="F37" s="137"/>
       <c r="G37" s="137"/>
-      <c r="H37" s="241">
+      <c r="H37" s="73">
         <v>93200</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="80" t="s">
-        <v>143</v>
+    <row r="38" spans="1:11">
+      <c r="A38" s="137" t="s">
+        <v>69</v>
       </c>
       <c r="B38" s="137"/>
       <c r="C38" s="137"/>
@@ -2736,127 +2714,126 @@
       <c r="F38" s="137"/>
       <c r="G38" s="137"/>
       <c r="H38" s="73">
-        <v>200000</v>
-      </c>
-      <c r="I38" s="7"/>
-    </row>
-    <row r="39" spans="1:9" ht="15.6" customHeight="1">
-      <c r="A39" s="215" t="s">
+        <v>33600.61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="81" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" s="82"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="186"/>
+      <c r="H39" s="73">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="81" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" s="82"/>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="186"/>
+      <c r="H40" s="73">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="137" t="s">
         <v>150</v>
       </c>
-      <c r="B39" s="216"/>
-      <c r="C39" s="216"/>
-      <c r="D39" s="216"/>
-      <c r="E39" s="216"/>
-      <c r="F39" s="216"/>
-      <c r="G39" s="217"/>
-      <c r="H39" s="73">
-        <f>71000+75400+57100</f>
-        <v>203500</v>
-      </c>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="137" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="137"/>
-      <c r="C40" s="137"/>
-      <c r="D40" s="137"/>
-      <c r="E40" s="137"/>
-      <c r="F40" s="137"/>
-      <c r="G40" s="137"/>
-      <c r="H40" s="241">
-        <v>33600.61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41" s="82"/>
-      <c r="C41" s="82"/>
-      <c r="D41" s="82"/>
-      <c r="E41" s="82"/>
-      <c r="F41" s="82"/>
-      <c r="G41" s="186"/>
+      <c r="B41" s="137"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="137"/>
+      <c r="E41" s="137"/>
+      <c r="F41" s="137"/>
+      <c r="G41" s="137"/>
       <c r="H41" s="73">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="81" t="s">
-        <v>160</v>
-      </c>
-      <c r="B42" s="82"/>
-      <c r="C42" s="82"/>
-      <c r="D42" s="82"/>
-      <c r="E42" s="82"/>
-      <c r="F42" s="82"/>
-      <c r="G42" s="186"/>
-      <c r="H42" s="241">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="81" t="s">
-        <v>161</v>
-      </c>
-      <c r="B43" s="82"/>
-      <c r="C43" s="82"/>
-      <c r="D43" s="82"/>
-      <c r="E43" s="82"/>
-      <c r="F43" s="82"/>
-      <c r="G43" s="186"/>
-      <c r="H43" s="241">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="37.950000000000003" customHeight="1">
-      <c r="A44" s="242" t="s">
-        <v>159</v>
-      </c>
-      <c r="B44" s="243"/>
-      <c r="C44" s="243"/>
-      <c r="D44" s="243"/>
-      <c r="E44" s="243"/>
-      <c r="F44" s="243"/>
-      <c r="G44" s="244"/>
-      <c r="H44" s="241">
-        <v>280000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="137" t="s">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="137" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" s="137"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="137"/>
+      <c r="G42" s="137"/>
+      <c r="H42" s="73">
+        <v>413700</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="137" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="137"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="137"/>
+      <c r="G43" s="137"/>
+      <c r="H43" s="69">
+        <f>SUM(H37:H42)</f>
+        <v>760500.61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="215" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="215"/>
+      <c r="C44" s="215"/>
+      <c r="D44" s="215"/>
+      <c r="E44" s="215"/>
+      <c r="F44" s="215"/>
+      <c r="G44" s="215"/>
+      <c r="H44" s="215"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="80" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="80"/>
+      <c r="C45" s="80"/>
+      <c r="D45" s="80"/>
+      <c r="E45" s="80"/>
+      <c r="F45" s="80"/>
+      <c r="G45" s="80"/>
+      <c r="H45" s="73">
+        <v>209000</v>
+      </c>
+      <c r="J45" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="137"/>
-      <c r="C45" s="137"/>
-      <c r="D45" s="137"/>
-      <c r="E45" s="137"/>
-      <c r="F45" s="137"/>
-      <c r="G45" s="137"/>
-      <c r="H45" s="241">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="137" t="s">
-        <v>158</v>
-      </c>
-      <c r="B46" s="137"/>
-      <c r="C46" s="137"/>
-      <c r="D46" s="137"/>
-      <c r="E46" s="137"/>
-      <c r="F46" s="137"/>
-      <c r="G46" s="137"/>
-      <c r="H46" s="241">
-        <v>413700</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="80" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" s="80"/>
+      <c r="C46" s="80"/>
+      <c r="D46" s="80"/>
+      <c r="E46" s="80"/>
+      <c r="F46" s="80"/>
+      <c r="G46" s="80"/>
+      <c r="H46" s="73">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="137" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B47" s="137"/>
       <c r="C47" s="137"/>
@@ -2864,85 +2841,79 @@
       <c r="E47" s="137"/>
       <c r="F47" s="137"/>
       <c r="G47" s="137"/>
-      <c r="H47" s="69">
-        <f>SUM(H37:H46)</f>
-        <v>1489000.6099999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="220" t="s">
-        <v>129</v>
-      </c>
-      <c r="B48" s="220"/>
-      <c r="C48" s="220"/>
-      <c r="D48" s="220"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="137" t="s">
-        <v>70</v>
-      </c>
-      <c r="B49" s="137"/>
-      <c r="C49" s="137"/>
-      <c r="D49" s="137"/>
-      <c r="E49" s="137"/>
-      <c r="F49" s="137"/>
-      <c r="G49" s="137"/>
+      <c r="H47" s="175">
+        <f>SUM(H45:H46)</f>
+        <v>259000</v>
+      </c>
+      <c r="K47" s="7"/>
+    </row>
+    <row r="48" spans="1:11" s="6" customFormat="1">
+      <c r="A48" s="187" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="188"/>
+      <c r="C48" s="188"/>
+      <c r="D48" s="188"/>
+      <c r="E48" s="188"/>
+      <c r="F48" s="188"/>
+      <c r="G48" s="188"/>
+      <c r="H48" s="189"/>
+    </row>
+    <row r="49" spans="1:9" s="6" customFormat="1">
+      <c r="A49" s="80" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" s="80"/>
+      <c r="C49" s="80"/>
+      <c r="D49" s="80"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="80"/>
       <c r="H49" s="73">
-        <v>189700</v>
-      </c>
-      <c r="J49" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="137" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" s="137"/>
-      <c r="C50" s="137"/>
-      <c r="D50" s="137"/>
-      <c r="E50" s="137"/>
-      <c r="F50" s="137"/>
-      <c r="G50" s="137"/>
-      <c r="H50" s="241">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="137" t="s">
-        <v>72</v>
-      </c>
-      <c r="B51" s="137"/>
-      <c r="C51" s="137"/>
-      <c r="D51" s="137"/>
-      <c r="E51" s="137"/>
-      <c r="F51" s="137"/>
-      <c r="G51" s="137"/>
-      <c r="H51" s="175">
-        <f>SUM(H49:H50)</f>
-        <v>239700</v>
-      </c>
-      <c r="K51" s="7"/>
-    </row>
-    <row r="52" spans="1:11" s="6" customFormat="1">
-      <c r="A52" s="221" t="s">
-        <v>130</v>
-      </c>
-      <c r="B52" s="222"/>
-      <c r="C52" s="222"/>
-      <c r="D52" s="222"/>
-      <c r="E52" s="222"/>
-      <c r="F52" s="222"/>
-      <c r="G52" s="222"/>
-      <c r="H52" s="223"/>
-    </row>
-    <row r="53" spans="1:11" s="6" customFormat="1">
+        <v>28834</v>
+      </c>
+      <c r="I49" s="60"/>
+    </row>
+    <row r="50" spans="1:9" s="6" customFormat="1">
+      <c r="A50" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="80"/>
+      <c r="C50" s="80"/>
+      <c r="D50" s="80"/>
+      <c r="E50" s="80"/>
+      <c r="F50" s="80"/>
+      <c r="G50" s="80"/>
+      <c r="H50" s="69">
+        <f>SUM(H49)</f>
+        <v>28834</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="6" customFormat="1">
+      <c r="A51" s="215" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="215"/>
+      <c r="C51" s="215"/>
+      <c r="D51" s="215"/>
+      <c r="E51" s="215"/>
+      <c r="F51" s="215"/>
+      <c r="G51" s="215"/>
+      <c r="H51" s="215"/>
+    </row>
+    <row r="52" spans="1:9" s="6" customFormat="1">
+      <c r="A52" s="80"/>
+      <c r="B52" s="80"/>
+      <c r="C52" s="80"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="80"/>
+      <c r="G52" s="80"/>
+      <c r="H52" s="73"/>
+    </row>
+    <row r="53" spans="1:9" s="6" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="80" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="B53" s="80"/>
       <c r="C53" s="80"/>
@@ -2950,657 +2921,589 @@
       <c r="E53" s="80"/>
       <c r="F53" s="80"/>
       <c r="G53" s="80"/>
-      <c r="H53" s="241">
-        <v>28834</v>
+      <c r="H53" s="69">
+        <f>SUM(H52:H52)</f>
+        <v>0</v>
       </c>
       <c r="I53" s="60"/>
     </row>
-    <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="80" t="s">
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A54" s="187"/>
+      <c r="B54" s="188"/>
+      <c r="C54" s="188"/>
+      <c r="D54" s="188"/>
+      <c r="E54" s="188"/>
+      <c r="F54" s="188"/>
+      <c r="G54" s="188"/>
+      <c r="H54" s="189"/>
+    </row>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A55" s="81"/>
+      <c r="B55" s="82"/>
+      <c r="C55" s="82"/>
+      <c r="D55" s="82"/>
+      <c r="E55" s="82"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A56" s="157"/>
+      <c r="B56" s="158"/>
+      <c r="C56" s="158"/>
+      <c r="D56" s="158"/>
+      <c r="E56" s="158"/>
+      <c r="F56" s="158"/>
+      <c r="G56" s="158"/>
+      <c r="H56" s="159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A57" s="160"/>
+      <c r="B57" s="161"/>
+      <c r="C57" s="161"/>
+      <c r="D57" s="161"/>
+      <c r="E57" s="161"/>
+      <c r="F57" s="161"/>
+      <c r="G57" s="161"/>
+      <c r="H57" s="156">
+        <f>H55+H56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A58" s="193" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="194"/>
+      <c r="C58" s="194"/>
+      <c r="D58" s="194"/>
+      <c r="E58" s="194"/>
+      <c r="F58" s="194"/>
+      <c r="G58" s="194"/>
+      <c r="H58" s="162">
+        <f>H53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A59" s="198"/>
+      <c r="B59" s="198"/>
+      <c r="C59" s="198"/>
+      <c r="D59" s="198"/>
+      <c r="E59" s="198"/>
+      <c r="F59" s="198"/>
+      <c r="G59" s="198"/>
+      <c r="H59" s="198"/>
+    </row>
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A60" s="199"/>
+      <c r="B60" s="199"/>
+      <c r="C60" s="199"/>
+      <c r="D60" s="199"/>
+      <c r="E60" s="199"/>
+      <c r="F60" s="199"/>
+      <c r="G60" s="199"/>
+      <c r="H60" s="199"/>
+    </row>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A61" s="197" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="197"/>
+      <c r="C61" s="197"/>
+      <c r="D61" s="197"/>
+      <c r="E61" s="197"/>
+      <c r="F61" s="197"/>
+      <c r="G61" s="197"/>
+      <c r="H61" s="163"/>
+    </row>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A62" s="200" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" s="201"/>
+      <c r="C62" s="201"/>
+      <c r="D62" s="201"/>
+      <c r="E62" s="201"/>
+      <c r="F62" s="201"/>
+      <c r="G62" s="202"/>
+      <c r="H62" s="73">
+        <f>60583.82+96723.22+413203.1</f>
+        <v>570510.14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="6" customFormat="1">
+      <c r="A63" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="80"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="80"/>
-      <c r="H54" s="69">
-        <f>SUM(H53)</f>
-        <v>28834</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="220" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55" s="220"/>
-      <c r="C55" s="220"/>
-      <c r="D55" s="220"/>
-      <c r="E55" s="220"/>
-      <c r="F55" s="220"/>
-      <c r="G55" s="220"/>
-      <c r="H55" s="220"/>
-    </row>
-    <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="80" t="s">
-        <v>152</v>
-      </c>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="73">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" s="6" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A57" s="215" t="s">
-        <v>153</v>
-      </c>
-      <c r="B57" s="216"/>
-      <c r="C57" s="216"/>
-      <c r="D57" s="216"/>
-      <c r="E57" s="216"/>
-      <c r="F57" s="216"/>
-      <c r="G57" s="217"/>
-      <c r="H57" s="73">
-        <v>997000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A58" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="B58" s="80"/>
-      <c r="C58" s="80"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="80"/>
-      <c r="F58" s="80"/>
-      <c r="G58" s="80"/>
-      <c r="H58" s="69">
-        <f>SUM(H56:H57)</f>
-        <v>1097000</v>
-      </c>
-      <c r="I58" s="60"/>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A59" s="221"/>
-      <c r="B59" s="222"/>
-      <c r="C59" s="222"/>
-      <c r="D59" s="222"/>
-      <c r="E59" s="222"/>
-      <c r="F59" s="222"/>
-      <c r="G59" s="222"/>
-      <c r="H59" s="223"/>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A60" s="81"/>
-      <c r="B60" s="82"/>
-      <c r="C60" s="82"/>
-      <c r="D60" s="82"/>
-      <c r="E60" s="82"/>
-      <c r="F60" s="82"/>
-      <c r="G60" s="82"/>
-      <c r="H60" s="156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A61" s="157"/>
-      <c r="B61" s="158"/>
-      <c r="C61" s="158"/>
-      <c r="D61" s="158"/>
-      <c r="E61" s="158"/>
-      <c r="F61" s="158"/>
-      <c r="G61" s="158"/>
-      <c r="H61" s="159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A62" s="160"/>
-      <c r="B62" s="161"/>
-      <c r="C62" s="161"/>
-      <c r="D62" s="161"/>
-      <c r="E62" s="161"/>
-      <c r="F62" s="161"/>
-      <c r="G62" s="161"/>
-      <c r="H62" s="156">
-        <f>H60+H61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A63" s="224" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" s="225"/>
-      <c r="C63" s="225"/>
-      <c r="D63" s="225"/>
-      <c r="E63" s="225"/>
-      <c r="F63" s="225"/>
-      <c r="G63" s="225"/>
-      <c r="H63" s="162">
-        <f>H58</f>
-        <v>1097000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="227"/>
-      <c r="B64" s="227"/>
-      <c r="C64" s="227"/>
-      <c r="D64" s="227"/>
-      <c r="E64" s="227"/>
-      <c r="F64" s="227"/>
-      <c r="G64" s="227"/>
-      <c r="H64" s="227"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A65" s="228"/>
-      <c r="B65" s="228"/>
-      <c r="C65" s="228"/>
-      <c r="D65" s="228"/>
-      <c r="E65" s="228"/>
-      <c r="F65" s="228"/>
-      <c r="G65" s="228"/>
-      <c r="H65" s="228"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A66" s="226" t="s">
-        <v>82</v>
-      </c>
-      <c r="B66" s="226"/>
-      <c r="C66" s="226"/>
-      <c r="D66" s="226"/>
-      <c r="E66" s="226"/>
-      <c r="F66" s="226"/>
-      <c r="G66" s="226"/>
-      <c r="H66" s="163"/>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A67" s="215"/>
-      <c r="B67" s="216"/>
-      <c r="C67" s="216"/>
-      <c r="D67" s="216"/>
-      <c r="E67" s="216"/>
-      <c r="F67" s="216"/>
-      <c r="G67" s="217"/>
-      <c r="H67" s="73"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A68" s="127" t="s">
-        <v>73</v>
-      </c>
-      <c r="B68" s="80"/>
-      <c r="C68" s="80"/>
-      <c r="D68" s="80"/>
-      <c r="E68" s="80"/>
-      <c r="F68" s="80"/>
-      <c r="G68" s="80"/>
-      <c r="H68" s="69">
-        <f>SUM(H67:H67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A69" s="128"/>
-      <c r="B69" s="128"/>
-      <c r="C69" s="128"/>
-      <c r="D69" s="128"/>
-      <c r="E69" s="128"/>
-      <c r="F69" s="128"/>
-      <c r="G69" s="128"/>
-      <c r="H69" s="129"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="194" t="s">
+      <c r="B63" s="80"/>
+      <c r="C63" s="80"/>
+      <c r="D63" s="80"/>
+      <c r="E63" s="80"/>
+      <c r="F63" s="80"/>
+      <c r="G63" s="80"/>
+      <c r="H63" s="69">
+        <f>SUM(H62)</f>
+        <v>570510.14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A64" s="128"/>
+      <c r="B64" s="128"/>
+      <c r="C64" s="128"/>
+      <c r="D64" s="128"/>
+      <c r="E64" s="128"/>
+      <c r="F64" s="128"/>
+      <c r="G64" s="128"/>
+      <c r="H64" s="129"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A65" s="195" t="s">
         <v>81</v>
       </c>
-      <c r="B70" s="195"/>
-      <c r="C70" s="195"/>
-      <c r="D70" s="195"/>
-      <c r="E70" s="195"/>
-      <c r="F70" s="195"/>
-      <c r="G70" s="195"/>
-      <c r="H70" s="130">
-        <f>H68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A71" s="210" t="s">
+      <c r="B65" s="196"/>
+      <c r="C65" s="196"/>
+      <c r="D65" s="196"/>
+      <c r="E65" s="196"/>
+      <c r="F65" s="196"/>
+      <c r="G65" s="196"/>
+      <c r="H65" s="130">
+        <f>H63</f>
+        <v>570510.14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A66" s="190" t="s">
         <v>87</v>
       </c>
-      <c r="B71" s="211"/>
-      <c r="C71" s="211"/>
-      <c r="D71" s="211"/>
-      <c r="E71" s="211"/>
-      <c r="F71" s="211"/>
-      <c r="G71" s="212"/>
-      <c r="H71" s="130">
-        <f>3283892.26-2477720.36</f>
-        <v>806171.89999999991</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A72" s="210" t="s">
+      <c r="B66" s="191"/>
+      <c r="C66" s="191"/>
+      <c r="D66" s="191"/>
+      <c r="E66" s="191"/>
+      <c r="F66" s="191"/>
+      <c r="G66" s="192"/>
+      <c r="H66" s="130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A67" s="190" t="s">
         <v>92</v>
       </c>
-      <c r="B72" s="211"/>
-      <c r="C72" s="211"/>
-      <c r="D72" s="211"/>
-      <c r="E72" s="211"/>
-      <c r="F72" s="211"/>
-      <c r="G72" s="212"/>
-      <c r="H72" s="130"/>
-    </row>
-    <row r="73" spans="1:11" ht="18">
-      <c r="A73" s="194" t="s">
+      <c r="B67" s="191"/>
+      <c r="C67" s="191"/>
+      <c r="D67" s="191"/>
+      <c r="E67" s="191"/>
+      <c r="F67" s="191"/>
+      <c r="G67" s="192"/>
+      <c r="H67" s="130"/>
+    </row>
+    <row r="68" spans="1:11" ht="18.75">
+      <c r="A68" s="195" t="s">
         <v>88</v>
       </c>
-      <c r="B73" s="195"/>
-      <c r="C73" s="195"/>
-      <c r="D73" s="195"/>
-      <c r="E73" s="195"/>
-      <c r="F73" s="195"/>
-      <c r="G73" s="195"/>
-      <c r="H73" s="130">
-        <f>H26+H35+H47+H51+H54+H31+H18+H22</f>
-        <v>2828746.7</v>
-      </c>
-      <c r="J73" s="171"/>
-      <c r="K73" s="142"/>
-    </row>
-    <row r="74" spans="1:11" ht="18">
-      <c r="A74" s="200" t="s">
+      <c r="B68" s="196"/>
+      <c r="C68" s="196"/>
+      <c r="D68" s="196"/>
+      <c r="E68" s="196"/>
+      <c r="F68" s="196"/>
+      <c r="G68" s="196"/>
+      <c r="H68" s="130">
+        <f>H26+H35+H43+H47+H50+H31+H18+H22</f>
+        <v>1934410.7</v>
+      </c>
+      <c r="J68" s="171"/>
+      <c r="K68" s="142"/>
+    </row>
+    <row r="69" spans="1:11" ht="18.75">
+      <c r="A69" s="226" t="s">
         <v>119</v>
       </c>
-      <c r="B74" s="201"/>
-      <c r="C74" s="201"/>
-      <c r="D74" s="201"/>
-      <c r="E74" s="201"/>
-      <c r="F74" s="201"/>
-      <c r="G74" s="202"/>
-      <c r="H74" s="131">
-        <f>H71+H73</f>
-        <v>3634918.6</v>
-      </c>
-      <c r="I74" s="126"/>
-      <c r="J74" s="209"/>
-      <c r="K74" s="209"/>
-    </row>
-    <row r="75" spans="1:11" ht="18">
-      <c r="A75" s="200" t="s">
+      <c r="B69" s="227"/>
+      <c r="C69" s="227"/>
+      <c r="D69" s="227"/>
+      <c r="E69" s="227"/>
+      <c r="F69" s="227"/>
+      <c r="G69" s="228"/>
+      <c r="H69" s="131">
+        <f>H66+H68</f>
+        <v>1934410.7</v>
+      </c>
+      <c r="I69" s="126"/>
+      <c r="J69" s="209"/>
+      <c r="K69" s="209"/>
+    </row>
+    <row r="70" spans="1:11" ht="18.75">
+      <c r="A70" s="226" t="s">
         <v>93</v>
       </c>
-      <c r="B75" s="201"/>
-      <c r="C75" s="201"/>
-      <c r="D75" s="201"/>
-      <c r="E75" s="201"/>
-      <c r="F75" s="201"/>
-      <c r="G75" s="202"/>
-      <c r="H75" s="132">
-        <f>H72+H70</f>
-        <v>0</v>
-      </c>
-      <c r="J75" s="142"/>
-    </row>
-    <row r="76" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A76" s="198" t="s">
+      <c r="B70" s="227"/>
+      <c r="C70" s="227"/>
+      <c r="D70" s="227"/>
+      <c r="E70" s="227"/>
+      <c r="F70" s="227"/>
+      <c r="G70" s="228"/>
+      <c r="H70" s="132">
+        <f>H67+H65</f>
+        <v>570510.14</v>
+      </c>
+      <c r="J70" s="142"/>
+    </row>
+    <row r="71" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A71" s="224" t="s">
         <v>83</v>
       </c>
-      <c r="B76" s="199"/>
-      <c r="C76" s="199"/>
-      <c r="D76" s="199"/>
-      <c r="E76" s="199"/>
-      <c r="F76" s="199"/>
-      <c r="G76" s="199"/>
-      <c r="H76" s="133">
-        <f>H73+H70</f>
-        <v>2828746.7</v>
-      </c>
-      <c r="J76" s="7"/>
-    </row>
-    <row r="77" spans="1:11" ht="18" hidden="1">
-      <c r="A77" s="196" t="s">
+      <c r="B71" s="225"/>
+      <c r="C71" s="225"/>
+      <c r="D71" s="225"/>
+      <c r="E71" s="225"/>
+      <c r="F71" s="225"/>
+      <c r="G71" s="225"/>
+      <c r="H71" s="133">
+        <f>H68+H65</f>
+        <v>2504920.84</v>
+      </c>
+      <c r="J71" s="7"/>
+    </row>
+    <row r="72" spans="1:11" ht="18.75" hidden="1">
+      <c r="A72" s="222" t="s">
         <v>17</v>
       </c>
-      <c r="B77" s="197"/>
-      <c r="C77" s="197"/>
-      <c r="D77" s="197"/>
-      <c r="E77" s="197"/>
-      <c r="F77" s="197"/>
-      <c r="G77" s="197"/>
-      <c r="H77" s="134">
-        <f>H62</f>
-        <v>0</v>
-      </c>
-      <c r="J77" s="7"/>
-    </row>
-    <row r="78" spans="1:11" ht="18" hidden="1">
-      <c r="A78" s="135"/>
-      <c r="B78" s="135"/>
-      <c r="C78" s="135"/>
-      <c r="D78" s="135"/>
-      <c r="E78" s="135"/>
-      <c r="F78" s="135"/>
-      <c r="G78" s="135"/>
-      <c r="H78" s="136"/>
-      <c r="J78" s="7"/>
-    </row>
-    <row r="79" spans="1:11" ht="18" hidden="1">
-      <c r="A79" s="135"/>
-      <c r="B79" s="135"/>
-      <c r="C79" s="135"/>
-      <c r="D79" s="135"/>
-      <c r="E79" s="135"/>
-      <c r="F79" s="135"/>
-      <c r="G79" s="135"/>
-      <c r="H79" s="136"/>
-      <c r="J79" s="7"/>
-    </row>
-    <row r="80" spans="1:11" ht="18" hidden="1">
-      <c r="A80" s="135"/>
-      <c r="B80" s="135"/>
-      <c r="C80" s="135"/>
-      <c r="D80" s="135"/>
-      <c r="E80" s="135"/>
-      <c r="F80" s="135"/>
-      <c r="G80" s="135"/>
-      <c r="H80" s="136"/>
-      <c r="J80" s="7"/>
-    </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A81" s="137"/>
-      <c r="B81" s="137"/>
-      <c r="C81" s="137"/>
-      <c r="D81" s="137"/>
-      <c r="E81" s="137"/>
-      <c r="F81" s="137"/>
-      <c r="G81" s="137"/>
-      <c r="H81" s="137"/>
-    </row>
-    <row r="82" spans="1:11" ht="18">
-      <c r="A82" s="191" t="s">
+      <c r="B72" s="223"/>
+      <c r="C72" s="223"/>
+      <c r="D72" s="223"/>
+      <c r="E72" s="223"/>
+      <c r="F72" s="223"/>
+      <c r="G72" s="223"/>
+      <c r="H72" s="134">
+        <f>H57</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="7"/>
+    </row>
+    <row r="73" spans="1:11" ht="18.75" hidden="1">
+      <c r="A73" s="135"/>
+      <c r="B73" s="135"/>
+      <c r="C73" s="135"/>
+      <c r="D73" s="135"/>
+      <c r="E73" s="135"/>
+      <c r="F73" s="135"/>
+      <c r="G73" s="135"/>
+      <c r="H73" s="136"/>
+      <c r="J73" s="7"/>
+    </row>
+    <row r="74" spans="1:11" ht="18.75" hidden="1">
+      <c r="A74" s="135"/>
+      <c r="B74" s="135"/>
+      <c r="C74" s="135"/>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="135"/>
+      <c r="H74" s="136"/>
+      <c r="J74" s="7"/>
+    </row>
+    <row r="75" spans="1:11" ht="18.75" hidden="1">
+      <c r="A75" s="135"/>
+      <c r="B75" s="135"/>
+      <c r="C75" s="135"/>
+      <c r="D75" s="135"/>
+      <c r="E75" s="135"/>
+      <c r="F75" s="135"/>
+      <c r="G75" s="135"/>
+      <c r="H75" s="136"/>
+      <c r="J75" s="7"/>
+    </row>
+    <row r="76" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A76" s="137"/>
+      <c r="B76" s="137"/>
+      <c r="C76" s="137"/>
+      <c r="D76" s="137"/>
+      <c r="E76" s="137"/>
+      <c r="F76" s="137"/>
+      <c r="G76" s="137"/>
+      <c r="H76" s="137"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.75">
+      <c r="A77" s="219" t="s">
         <v>10</v>
       </c>
-      <c r="B82" s="192"/>
-      <c r="C82" s="192"/>
-      <c r="D82" s="192"/>
-      <c r="E82" s="192"/>
-      <c r="F82" s="192"/>
-      <c r="G82" s="192"/>
-      <c r="H82" s="193"/>
-    </row>
-    <row r="83" spans="1:11" ht="18">
-      <c r="A83" s="138" t="s">
+      <c r="B77" s="220"/>
+      <c r="C77" s="220"/>
+      <c r="D77" s="220"/>
+      <c r="E77" s="220"/>
+      <c r="F77" s="220"/>
+      <c r="G77" s="220"/>
+      <c r="H77" s="221"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75">
+      <c r="A78" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="B83" s="139"/>
-      <c r="C83" s="139"/>
-      <c r="D83" s="139"/>
-      <c r="E83" s="139"/>
-      <c r="F83" s="139"/>
-      <c r="G83" s="139"/>
-      <c r="H83" s="140">
-        <v>4724122.12</v>
-      </c>
+      <c r="B78" s="139"/>
+      <c r="C78" s="139"/>
+      <c r="D78" s="139"/>
+      <c r="E78" s="139"/>
+      <c r="F78" s="139"/>
+      <c r="G78" s="139"/>
+      <c r="H78" s="140">
+        <v>4229401.2367692199</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" s="81" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" s="82"/>
+      <c r="C79" s="82"/>
+      <c r="D79" s="82"/>
+      <c r="E79" s="82"/>
+      <c r="F79" s="82"/>
+      <c r="G79" s="82"/>
+      <c r="H79" s="141">
+        <f>Planilla!G32</f>
+        <v>3689620.7905269074</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" s="79"/>
+      <c r="C80" s="79"/>
+      <c r="D80" s="79"/>
+      <c r="E80" s="79"/>
+      <c r="F80" s="79"/>
+      <c r="G80" s="79"/>
+      <c r="H80" s="179">
+        <f>-(H71)</f>
+        <v>-2504920.84</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="79"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="79"/>
+      <c r="E81" s="79"/>
+      <c r="F81" s="79"/>
+      <c r="G81" s="79"/>
+      <c r="H81" s="179">
+        <f>-H58</f>
+        <v>0</v>
+      </c>
+      <c r="K81" s="6"/>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="78" t="s">
+        <v>143</v>
+      </c>
+      <c r="B82" s="79"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="79"/>
+      <c r="F82" s="79"/>
+      <c r="G82" s="79"/>
+      <c r="H82" s="121">
+        <f>217300-H83</f>
+        <v>154086</v>
+      </c>
+      <c r="J82" s="7"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="B83" s="79"/>
+      <c r="C83" s="79"/>
+      <c r="D83" s="79"/>
+      <c r="E83" s="79"/>
+      <c r="F83" s="79"/>
+      <c r="G83" s="79"/>
+      <c r="H83" s="121">
+        <v>63214</v>
+      </c>
+      <c r="I83" s="142"/>
+      <c r="J83" s="7"/>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="81" t="s">
-        <v>145</v>
-      </c>
-      <c r="B84" s="82"/>
-      <c r="C84" s="82"/>
-      <c r="D84" s="82"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="141">
-        <f>Planilla!G32</f>
-        <v>2867785.4767692201</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="78" t="s">
-        <v>157</v>
-      </c>
-      <c r="B85" s="79"/>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
-      <c r="F85" s="79"/>
-      <c r="G85" s="79"/>
-      <c r="H85" s="179">
-        <f>-(H76)</f>
-        <v>-2828746.7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="B86" s="79"/>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
-      <c r="E86" s="79"/>
-      <c r="F86" s="79"/>
-      <c r="G86" s="79"/>
-      <c r="H86" s="179">
-        <f>-H63</f>
-        <v>-1097000</v>
-      </c>
-      <c r="K86" s="6"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="78" t="s">
-        <v>144</v>
-      </c>
-      <c r="B87" s="79"/>
-      <c r="C87" s="79"/>
-      <c r="D87" s="79"/>
-      <c r="E87" s="79"/>
-      <c r="F87" s="79"/>
-      <c r="G87" s="79"/>
-      <c r="H87" s="121">
-        <v>154000</v>
-      </c>
-      <c r="J87" s="7"/>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="B88" s="79"/>
-      <c r="C88" s="79"/>
-      <c r="D88" s="79"/>
-      <c r="E88" s="79"/>
-      <c r="F88" s="79"/>
-      <c r="G88" s="79"/>
-      <c r="H88" s="121">
-        <v>63214</v>
-      </c>
-      <c r="I88" s="142"/>
-      <c r="J88" s="7"/>
+      <c r="A84" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B84" s="83"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="98"/>
+    </row>
+    <row r="85" spans="1:11" ht="18.75">
+      <c r="A85" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="23"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="23"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="23"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="84">
+        <f>SUM(H78:H84)</f>
+        <v>5631401.1872961279</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="87" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A87" s="216" t="s">
+        <v>97</v>
+      </c>
+      <c r="B87" s="217"/>
+      <c r="C87" s="217"/>
+      <c r="D87" s="217"/>
+      <c r="E87" s="217"/>
+      <c r="F87" s="217"/>
+      <c r="G87" s="217"/>
+      <c r="H87" s="218"/>
+    </row>
+    <row r="88" spans="1:11" ht="15.75">
+      <c r="A88" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" s="87"/>
+      <c r="C88" s="87"/>
+      <c r="D88" s="87"/>
+      <c r="E88" s="87"/>
+      <c r="F88" s="87"/>
+      <c r="G88" s="87"/>
+      <c r="H88" s="88">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B89" s="83"/>
+      <c r="A89" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="B89" s="91"/>
       <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="98"/>
-    </row>
-    <row r="90" spans="1:11" ht="18">
-      <c r="A90" s="22" t="s">
+      <c r="D89" s="61"/>
+      <c r="E89" s="61"/>
+      <c r="F89" s="61"/>
+      <c r="G89" s="61"/>
+      <c r="H89" s="125"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="61"/>
+      <c r="B90" s="97"/>
+      <c r="C90" s="61"/>
+      <c r="D90" s="61"/>
+      <c r="E90" s="61"/>
+      <c r="F90" s="61"/>
+      <c r="G90" s="61"/>
+      <c r="H90" s="21"/>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="61"/>
+      <c r="B91" s="61"/>
+      <c r="C91" s="61"/>
+      <c r="D91" s="61"/>
+      <c r="E91" s="61"/>
+      <c r="F91" s="61"/>
+      <c r="G91" s="61"/>
+      <c r="H91" s="21"/>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="84">
-        <f>SUM(H83:H89)</f>
-        <v>3883374.89676922</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="15" thickBot="1"/>
-    <row r="92" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A92" s="188" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="189"/>
-      <c r="C92" s="189"/>
-      <c r="D92" s="189"/>
-      <c r="E92" s="189"/>
-      <c r="F92" s="189"/>
-      <c r="G92" s="189"/>
-      <c r="H92" s="190"/>
-    </row>
-    <row r="93" spans="1:11" ht="15.6">
-      <c r="A93" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" s="87"/>
-      <c r="C93" s="87"/>
-      <c r="D93" s="87"/>
-      <c r="E93" s="87"/>
-      <c r="F93" s="87"/>
-      <c r="G93" s="87"/>
-      <c r="H93" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="B94" s="91"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="125"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="61"/>
-      <c r="B95" s="97"/>
-      <c r="C95" s="61"/>
-      <c r="D95" s="61"/>
-      <c r="E95" s="61"/>
-      <c r="F95" s="61"/>
-      <c r="G95" s="61"/>
-      <c r="H95" s="21"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="61"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61"/>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="21"/>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="B97" s="85"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="85"/>
-      <c r="E97" s="85"/>
-      <c r="F97" s="85"/>
-      <c r="G97" s="85"/>
-      <c r="H97" s="86">
-        <f>SUM(H93:H96)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="187"/>
-      <c r="B100" s="187"/>
-      <c r="C100" s="187"/>
-      <c r="D100" s="187"/>
-      <c r="E100" s="187"/>
-      <c r="F100" s="187"/>
-      <c r="G100" s="187"/>
-      <c r="H100" s="187"/>
-    </row>
-    <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="187"/>
-      <c r="B101" s="187"/>
-      <c r="C101" s="187"/>
-      <c r="D101" s="187"/>
-      <c r="E101" s="187"/>
-      <c r="F101" s="187"/>
-      <c r="G101" s="187"/>
-      <c r="H101" s="187"/>
-    </row>
-    <row r="102" spans="1:8" hidden="1">
-      <c r="A102" s="187"/>
-      <c r="B102" s="187"/>
-      <c r="C102" s="187"/>
-      <c r="D102" s="187"/>
-      <c r="E102" s="187"/>
-      <c r="F102" s="187"/>
-      <c r="G102" s="187"/>
-      <c r="H102" s="187"/>
-    </row>
-    <row r="103" spans="1:8" hidden="1">
-      <c r="A103" s="187"/>
-      <c r="B103" s="187"/>
-      <c r="C103" s="187"/>
-      <c r="D103" s="187"/>
-      <c r="E103" s="187"/>
-      <c r="F103" s="187"/>
-      <c r="G103" s="187"/>
-      <c r="H103" s="187"/>
+      <c r="B92" s="85"/>
+      <c r="C92" s="85"/>
+      <c r="D92" s="85"/>
+      <c r="E92" s="85"/>
+      <c r="F92" s="85"/>
+      <c r="G92" s="85"/>
+      <c r="H92" s="86">
+        <f>SUM(H88:H91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" hidden="1">
+      <c r="A95" s="213"/>
+      <c r="B95" s="213"/>
+      <c r="C95" s="213"/>
+      <c r="D95" s="213"/>
+      <c r="E95" s="213"/>
+      <c r="F95" s="213"/>
+      <c r="G95" s="213"/>
+      <c r="H95" s="213"/>
+    </row>
+    <row r="96" spans="1:11" hidden="1">
+      <c r="A96" s="213"/>
+      <c r="B96" s="213"/>
+      <c r="C96" s="213"/>
+      <c r="D96" s="213"/>
+      <c r="E96" s="213"/>
+      <c r="F96" s="213"/>
+      <c r="G96" s="213"/>
+      <c r="H96" s="213"/>
+    </row>
+    <row r="97" spans="1:8" hidden="1">
+      <c r="A97" s="213"/>
+      <c r="B97" s="213"/>
+      <c r="C97" s="213"/>
+      <c r="D97" s="213"/>
+      <c r="E97" s="213"/>
+      <c r="F97" s="213"/>
+      <c r="G97" s="213"/>
+      <c r="H97" s="213"/>
+    </row>
+    <row r="98" spans="1:8" hidden="1">
+      <c r="A98" s="213"/>
+      <c r="B98" s="213"/>
+      <c r="C98" s="213"/>
+      <c r="D98" s="213"/>
+      <c r="E98" s="213"/>
+      <c r="F98" s="213"/>
+      <c r="G98" s="213"/>
+      <c r="H98" s="213"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A52:H52"/>
+  <mergeCells count="29">
+    <mergeCell ref="A95:H98"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A63:G63"/>
     <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A64:H65"/>
-    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A69:G69"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="J69:K69"/>
+    <mergeCell ref="A67:G67"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A67:G67"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A100:H103"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A82:H82"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A59:H60"/>
+    <mergeCell ref="A62:G62"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3611,24 +3514,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3660,7 +3563,7 @@
       <c r="A2" s="61"/>
       <c r="B2" s="61"/>
       <c r="C2" s="124">
-        <v>3283892.26</v>
+        <v>1934410.7</v>
       </c>
       <c r="D2" s="61"/>
       <c r="E2" s="61"/>
@@ -3726,12 +3629,12 @@
       <c r="A5" s="120"/>
       <c r="B5" s="230">
         <f>C2</f>
-        <v>3283892.26</v>
+        <v>1934410.7</v>
       </c>
       <c r="C5" s="230"/>
       <c r="D5" s="21"/>
       <c r="E5" s="236">
-        <v>1097000</v>
+        <v>0</v>
       </c>
       <c r="F5" s="237"/>
       <c r="G5" s="114"/>
@@ -3750,7 +3653,7 @@
       <c r="C6" s="233"/>
       <c r="D6" s="21"/>
       <c r="E6" s="232" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F6" s="233"/>
       <c r="G6" s="114"/>
@@ -3768,7 +3671,9 @@
       <c r="B7" s="230"/>
       <c r="C7" s="230"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="234"/>
+      <c r="E7" s="234">
+        <v>570510</v>
+      </c>
       <c r="F7" s="235"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
@@ -3844,19 +3749,16 @@
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="98">
-        <v>146111.69953921993</v>
-      </c>
-      <c r="G9" s="176">
-        <f>F9</f>
-        <v>146111.69953921993</v>
-      </c>
+        <v>177426.13652999999</v>
+      </c>
+      <c r="G9" s="176"/>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>0</v>
+        <v>177426.13652999999</v>
       </c>
       <c r="I9" s="68">
         <f>H9*3.7%</f>
-        <v>0</v>
+        <v>6564.7670516100006</v>
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
@@ -3864,15 +3766,15 @@
       </c>
       <c r="K9" s="68">
         <f>E$5*E9</f>
-        <v>44428.5</v>
+        <v>0</v>
       </c>
       <c r="L9" s="68">
         <f>E$7*E9</f>
-        <v>0</v>
+        <v>23105.655000000002</v>
       </c>
       <c r="M9" s="168">
         <f>B$5*E9</f>
-        <v>132997.63652999999</v>
+        <v>78343.633350000004</v>
       </c>
       <c r="N9" s="168">
         <f>B$7*E9</f>
@@ -3880,7 +3782,7 @@
       </c>
       <c r="O9" s="183">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>177426.13652999999</v>
+        <v>285440.19193161</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -3898,11 +3800,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>231833.42164799996</v>
+        <v>283881.81844799995</v>
       </c>
       <c r="G10" s="176">
         <f>F10</f>
-        <v>231833.42164799996</v>
+        <v>283881.81844799995</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -3918,15 +3820,15 @@
       </c>
       <c r="K10" s="68">
         <f t="shared" ref="K10:K31" si="2">E$5*E10</f>
-        <v>71085.599999999991</v>
+        <v>0</v>
       </c>
       <c r="L10" s="68">
         <f t="shared" ref="L10:L31" si="3">E$7*E10</f>
-        <v>0</v>
+        <v>36969.047999999995</v>
       </c>
       <c r="M10" s="25">
         <f t="shared" ref="M10:M31" si="4">B$5*E10</f>
-        <v>212796.21844799997</v>
+        <v>125349.81335999999</v>
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
@@ -3934,7 +3836,7 @@
       </c>
       <c r="O10" s="183">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
-        <v>283881.81844799995</v>
+        <v>162318.86135999998</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
@@ -3954,11 +3856,11 @@
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="98">
-        <v>172443.99573199998</v>
+        <v>211159.00693199999</v>
       </c>
       <c r="G11" s="176">
         <f>F11</f>
-        <v>172443.99573199998</v>
+        <v>211159.00693199999</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -3974,15 +3876,15 @@
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
-        <v>52875.4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27498.581999999999</v>
       </c>
       <c r="M11" s="168">
         <f t="shared" si="4"/>
-        <v>158283.606932</v>
+        <v>93238.595740000004</v>
       </c>
       <c r="N11" s="168">
         <f t="shared" si="5"/>
@@ -3990,7 +3892,7 @@
       </c>
       <c r="O11" s="183">
         <f t="shared" si="6"/>
-        <v>211159.00693199999</v>
+        <v>120737.17774</v>
       </c>
       <c r="P11" s="171"/>
     </row>
@@ -4011,16 +3913,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="147">
-        <v>5525636.4477676637</v>
+        <v>5964462.7322450671</v>
       </c>
       <c r="G12" s="177"/>
       <c r="H12" s="148">
         <f t="shared" si="0"/>
-        <v>5525636.4477676637</v>
+        <v>5964462.7322450671</v>
       </c>
       <c r="I12" s="148">
         <f t="shared" si="7"/>
-        <v>204448.54856740357</v>
+        <v>220685.12109306752</v>
       </c>
       <c r="J12" s="148">
         <f t="shared" si="1"/>
@@ -4028,15 +3930,15 @@
       </c>
       <c r="K12" s="148">
         <f t="shared" si="2"/>
-        <v>58689.5</v>
+        <v>0</v>
       </c>
       <c r="L12" s="148">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30522.285</v>
       </c>
       <c r="M12" s="149">
         <f t="shared" si="4"/>
-        <v>175688.23590999999</v>
+        <v>103490.97245</v>
       </c>
       <c r="N12" s="149">
         <f t="shared" si="5"/>
@@ -4044,7 +3946,7 @@
       </c>
       <c r="O12" s="184">
         <f t="shared" si="6"/>
-        <v>5964462.7322450671</v>
+        <v>6319161.1107881349</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -4062,11 +3964,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>137740.53600999998</v>
+        <v>168664.35200999997</v>
       </c>
       <c r="G13" s="176">
         <f>F13</f>
-        <v>137740.53600999998</v>
+        <v>168664.35200999997</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -4082,15 +3984,15 @@
       </c>
       <c r="K13" s="68">
         <f t="shared" si="2"/>
-        <v>42234.5</v>
+        <v>0</v>
       </c>
       <c r="L13" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>21964.634999999998</v>
       </c>
       <c r="M13" s="25">
         <f t="shared" si="4"/>
-        <v>126429.85200999999</v>
+        <v>74474.811950000003</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
@@ -4098,7 +4000,7 @@
       </c>
       <c r="O13" s="183">
         <f t="shared" si="6"/>
-        <v>168664.35200999997</v>
+        <v>96439.446949999998</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4116,11 +4018,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="G14" s="176">
         <f>F14</f>
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
@@ -4136,15 +4038,15 @@
       </c>
       <c r="K14" s="68">
         <f t="shared" si="2"/>
-        <v>39382.300000000003</v>
+        <v>0</v>
       </c>
       <c r="L14" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20481.309000000001</v>
       </c>
       <c r="M14" s="25">
         <f t="shared" si="4"/>
-        <v>117891.73213399999</v>
+        <v>69445.344129999998</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
@@ -4152,7 +4054,7 @@
       </c>
       <c r="O14" s="183">
         <f t="shared" si="6"/>
-        <v>157274.03213399998</v>
+        <v>89926.653129999992</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -4172,11 +4074,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>148115.79716399999</v>
+        <v>181368.93956399997</v>
       </c>
       <c r="G15" s="176">
         <f>F15</f>
-        <v>148115.79716399999</v>
+        <v>181368.93956399997</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
@@ -4192,22 +4094,22 @@
       </c>
       <c r="K15" s="68">
         <f t="shared" si="2"/>
-        <v>45415.799999999996</v>
+        <v>0</v>
       </c>
       <c r="L15" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23619.114000000001</v>
       </c>
       <c r="M15" s="25">
         <f t="shared" si="4"/>
-        <v>135953.13956399998</v>
+        <v>80084.602979999996</v>
       </c>
       <c r="N15" s="25">
         <v>0</v>
       </c>
       <c r="O15" s="183">
         <f t="shared" si="6"/>
-        <v>181368.93956399997</v>
+        <v>103703.71698</v>
       </c>
       <c r="Q15" s="180"/>
     </row>
@@ -4228,11 +4130,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="G16" s="176">
         <f>F16</f>
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
@@ -4248,15 +4150,15 @@
       </c>
       <c r="K16" s="68">
         <f t="shared" si="2"/>
-        <v>58689.5</v>
+        <v>0</v>
       </c>
       <c r="L16" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30522.285</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" si="4"/>
-        <v>175688.23590999999</v>
+        <v>103490.97245</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
@@ -4264,7 +4166,7 @@
       </c>
       <c r="O16" s="183">
         <f t="shared" si="6"/>
-        <v>234377.73590999999</v>
+        <v>134013.25745</v>
       </c>
       <c r="Q16" s="180"/>
     </row>
@@ -4285,16 +4187,19 @@
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>240652.97185236996</v>
-      </c>
-      <c r="G17" s="176"/>
+        <v>418221.4838209076</v>
+      </c>
+      <c r="G17" s="176">
+        <f>F17</f>
+        <v>418221.4838209076</v>
+      </c>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
-        <v>240652.97185236996</v>
+        <v>0</v>
       </c>
       <c r="I17" s="24">
         <f t="shared" si="7"/>
-        <v>8904.1599585376898</v>
+        <v>0</v>
       </c>
       <c r="J17" s="24">
         <f t="shared" si="1"/>
@@ -4302,15 +4207,15 @@
       </c>
       <c r="K17" s="68">
         <f t="shared" si="2"/>
-        <v>42234.5</v>
+        <v>0</v>
       </c>
       <c r="L17" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>21964.634999999998</v>
       </c>
       <c r="M17" s="25">
         <f t="shared" si="4"/>
-        <v>126429.85200999999</v>
+        <v>74474.811950000003</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
@@ -4318,7 +4223,7 @@
       </c>
       <c r="O17" s="183">
         <f t="shared" si="6"/>
-        <v>418221.4838209076</v>
+        <v>96439.446949999998</v>
       </c>
       <c r="Q17" s="180"/>
     </row>
@@ -4337,10 +4242,10 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="98">
-        <v>23120.101368910371</v>
+        <v>-32805.866497089621</v>
       </c>
       <c r="G18" s="176">
-        <f>RESUMEN!H37+RESUMEN!H45+RESUMEN!H50</f>
+        <f>RESUMEN!H37+RESUMEN!H41+RESUMEN!H46</f>
         <v>218200</v>
       </c>
       <c r="H18" s="68">
@@ -4353,19 +4258,19 @@
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
-        <v>195079.89863108963</v>
+        <v>251005.86649708962</v>
       </c>
       <c r="K18" s="68">
         <f t="shared" si="2"/>
-        <v>39382.300000000003</v>
+        <v>0</v>
       </c>
       <c r="L18" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20481.309000000001</v>
       </c>
       <c r="M18" s="168">
         <f t="shared" si="4"/>
-        <v>117891.73213399999</v>
+        <v>69445.344129999998</v>
       </c>
       <c r="N18" s="168">
         <f t="shared" si="5"/>
@@ -4373,7 +4278,7 @@
       </c>
       <c r="O18" s="183">
         <f t="shared" si="6"/>
-        <v>-37805.866497089621</v>
+        <v>-161079.21336708963</v>
       </c>
       <c r="Q18" s="180"/>
     </row>
@@ -4394,16 +4299,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="147">
-        <v>3913085.233736075</v>
+        <v>4239238.3269483093</v>
       </c>
       <c r="G19" s="177"/>
       <c r="H19" s="148">
         <f t="shared" si="0"/>
-        <v>3913085.233736075</v>
+        <v>4239238.3269483093</v>
       </c>
       <c r="I19" s="148">
         <f t="shared" si="7"/>
-        <v>144784.15364823479</v>
+        <v>156851.81809708747</v>
       </c>
       <c r="J19" s="148">
         <f t="shared" si="1"/>
@@ -4411,15 +4316,15 @@
       </c>
       <c r="K19" s="148">
         <f t="shared" si="2"/>
-        <v>45415.799999999996</v>
+        <v>0</v>
       </c>
       <c r="L19" s="148">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23619.114000000001</v>
       </c>
       <c r="M19" s="149">
         <f t="shared" si="4"/>
-        <v>135953.13956399998</v>
+        <v>80084.602979999996</v>
       </c>
       <c r="N19" s="149">
         <f t="shared" si="5"/>
@@ -4427,7 +4332,7 @@
       </c>
       <c r="O19" s="184">
         <f t="shared" si="6"/>
-        <v>4239238.3269483093</v>
+        <v>4499793.8620253969</v>
       </c>
       <c r="Q19" s="180"/>
     </row>
@@ -4448,11 +4353,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="G20" s="176">
         <f>F20</f>
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -4468,15 +4373,15 @@
       </c>
       <c r="K20" s="68">
         <f t="shared" si="2"/>
-        <v>58689.5</v>
+        <v>0</v>
       </c>
       <c r="L20" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30522.285</v>
       </c>
       <c r="M20" s="25">
         <f t="shared" si="4"/>
-        <v>175688.23590999999</v>
+        <v>103490.97245</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
@@ -4484,7 +4389,7 @@
       </c>
       <c r="O20" s="183">
         <f t="shared" si="6"/>
-        <v>234377.73590999999</v>
+        <v>134013.25745</v>
       </c>
       <c r="Q20" s="180"/>
     </row>
@@ -4503,18 +4408,18 @@
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="147">
-        <v>1758103.0833163089</v>
+        <v>1991817.2494090125</v>
       </c>
       <c r="G21" s="178">
         <v>0</v>
       </c>
       <c r="H21" s="148">
         <f t="shared" si="0"/>
-        <v>1758103.0833163089</v>
+        <v>1991817.2494090125</v>
       </c>
       <c r="I21" s="148">
         <f t="shared" si="7"/>
-        <v>65049.814082703437</v>
+        <v>73697.238228133472</v>
       </c>
       <c r="J21" s="148">
         <f t="shared" si="1"/>
@@ -4522,15 +4427,15 @@
       </c>
       <c r="K21" s="148">
         <f t="shared" si="2"/>
-        <v>42234.5</v>
+        <v>0</v>
       </c>
       <c r="L21" s="148">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>21964.634999999998</v>
       </c>
       <c r="M21" s="149">
         <f t="shared" si="4"/>
-        <v>126429.85200999999</v>
+        <v>74474.811950000003</v>
       </c>
       <c r="N21" s="149">
         <f t="shared" si="5"/>
@@ -4538,7 +4443,7 @@
       </c>
       <c r="O21" s="184">
         <f t="shared" si="6"/>
-        <v>1991817.2494090125</v>
+        <v>2161953.9345871457</v>
       </c>
       <c r="Q21" s="180"/>
     </row>
@@ -4559,11 +4464,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="G22" s="176">
         <f>F22</f>
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
@@ -4579,15 +4484,15 @@
       </c>
       <c r="K22" s="68">
         <f t="shared" si="2"/>
-        <v>39382.300000000003</v>
+        <v>0</v>
       </c>
       <c r="L22" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20481.309000000001</v>
       </c>
       <c r="M22" s="25">
         <f t="shared" si="4"/>
-        <v>117891.73213399999</v>
+        <v>69445.344129999998</v>
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
@@ -4595,7 +4500,7 @@
       </c>
       <c r="O22" s="183">
         <f t="shared" si="6"/>
-        <v>157274.03213399998</v>
+        <v>89926.653129999992</v>
       </c>
       <c r="Q22" s="180"/>
     </row>
@@ -4616,11 +4521,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>148115.79716399999</v>
+        <v>181368.73672799996</v>
       </c>
       <c r="G23" s="176">
-        <f>135953+12163</f>
-        <v>148116</v>
+        <f>F23</f>
+        <v>181368.73672799996</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
@@ -4632,19 +4537,19 @@
       </c>
       <c r="J23" s="24">
         <f t="shared" si="1"/>
-        <v>0.20283600001130253</v>
+        <v>0</v>
       </c>
       <c r="K23" s="68">
         <f t="shared" si="2"/>
-        <v>45415.799999999996</v>
+        <v>0</v>
       </c>
       <c r="L23" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23619.114000000001</v>
       </c>
       <c r="M23" s="25">
         <f t="shared" si="4"/>
-        <v>135953.13956399998</v>
+        <v>80084.602979999996</v>
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
@@ -4652,7 +4557,7 @@
       </c>
       <c r="O23" s="183">
         <f t="shared" si="6"/>
-        <v>181368.73672799996</v>
+        <v>103703.71698</v>
       </c>
       <c r="Q23" s="180"/>
     </row>
@@ -4671,11 +4576,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="G24" s="176">
         <f>F24</f>
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
@@ -4691,15 +4596,15 @@
       </c>
       <c r="K24" s="68">
         <f t="shared" si="2"/>
-        <v>58689.5</v>
+        <v>0</v>
       </c>
       <c r="L24" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30522.285</v>
       </c>
       <c r="M24" s="25">
         <f t="shared" si="4"/>
-        <v>175688.23590999999</v>
+        <v>103490.97245</v>
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
@@ -4707,7 +4612,7 @@
       </c>
       <c r="O24" s="183">
         <f t="shared" si="6"/>
-        <v>234377.73590999999</v>
+        <v>134013.25745</v>
       </c>
       <c r="Q24" s="180"/>
     </row>
@@ -4728,11 +4633,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>137740.53600999998</v>
+        <v>168663.88801999995</v>
       </c>
       <c r="G25" s="176">
-        <f>126430+11311</f>
-        <v>137741</v>
+        <f>F25</f>
+        <v>168663.88801999995</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -4744,19 +4649,19 @@
       </c>
       <c r="J25" s="24">
         <f t="shared" si="1"/>
-        <v>0.46399000001838431</v>
+        <v>0</v>
       </c>
       <c r="K25" s="68">
         <f t="shared" si="2"/>
-        <v>42234.5</v>
+        <v>0</v>
       </c>
       <c r="L25" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>21964.634999999998</v>
       </c>
       <c r="M25" s="25">
         <f t="shared" si="4"/>
-        <v>126429.85200999999</v>
+        <v>74474.811950000003</v>
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
@@ -4764,7 +4669,7 @@
       </c>
       <c r="O25" s="183">
         <f t="shared" si="6"/>
-        <v>168663.88801999995</v>
+        <v>96439.446949999998</v>
       </c>
       <c r="Q25" s="181"/>
     </row>
@@ -4783,11 +4688,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="G26" s="176">
         <f>F26</f>
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -4803,15 +4708,15 @@
       </c>
       <c r="K26" s="68">
         <f t="shared" si="2"/>
-        <v>39382.300000000003</v>
+        <v>0</v>
       </c>
       <c r="L26" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20481.309000000001</v>
       </c>
       <c r="M26" s="25">
         <f t="shared" si="4"/>
-        <v>117891.73213399999</v>
+        <v>69445.344129999998</v>
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
@@ -4819,7 +4724,7 @@
       </c>
       <c r="O26" s="183">
         <f t="shared" si="6"/>
-        <v>157274.03213399998</v>
+        <v>89926.653129999992</v>
       </c>
       <c r="Q26" s="180"/>
     </row>
@@ -4840,18 +4745,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="147">
-        <v>3564415.7164625912</v>
+        <v>3724071.6003557066</v>
       </c>
       <c r="G27" s="177">
-        <v>148116.14000000001</v>
+        <v>181369.14</v>
       </c>
       <c r="H27" s="170">
         <f t="shared" si="0"/>
-        <v>3416299.5764625911</v>
+        <v>3542702.4603557065</v>
       </c>
       <c r="I27" s="148">
         <f t="shared" si="7"/>
-        <v>126403.08432911588</v>
+        <v>131079.99103316115</v>
       </c>
       <c r="J27" s="148">
         <f t="shared" si="1"/>
@@ -4859,15 +4764,15 @@
       </c>
       <c r="K27" s="148">
         <f t="shared" si="2"/>
-        <v>45415.799999999996</v>
+        <v>0</v>
       </c>
       <c r="L27" s="148">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23619.114000000001</v>
       </c>
       <c r="M27" s="149">
         <f t="shared" si="4"/>
-        <v>135953.13956399998</v>
+        <v>80084.602979999996</v>
       </c>
       <c r="N27" s="149">
         <f t="shared" si="5"/>
@@ -4875,11 +4780,11 @@
       </c>
       <c r="O27" s="184">
         <f t="shared" si="6"/>
-        <v>3724071.6003557066</v>
+        <v>3777486.1683688676</v>
       </c>
       <c r="P27" s="182">
         <f>M27+N27</f>
-        <v>135953.13956399998</v>
+        <v>80084.602979999996</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.25" customHeight="1">
@@ -4897,16 +4802,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>3041954.5174085847</v>
+        <v>3388884.5704627023</v>
       </c>
       <c r="G28" s="176"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>3041954.5174085847</v>
+        <v>3388884.5704627023</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="7"/>
-        <v>112552.31714411765</v>
+        <v>125388.72910712</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -4914,15 +4819,15 @@
       </c>
       <c r="K28" s="68">
         <f t="shared" si="2"/>
-        <v>58689.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30522.285</v>
       </c>
       <c r="M28" s="25">
         <f t="shared" si="4"/>
-        <v>175688.23590999999</v>
+        <v>103490.97245</v>
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
@@ -4930,7 +4835,7 @@
       </c>
       <c r="O28" s="183">
         <f t="shared" si="6"/>
-        <v>3388884.5704627023</v>
+        <v>3648286.5570198223</v>
       </c>
       <c r="P28" s="7"/>
     </row>
@@ -4949,11 +4854,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>137740.53600999998</v>
+        <v>168664.35200999997</v>
       </c>
       <c r="G29" s="176">
         <f>F29</f>
-        <v>137740.53600999998</v>
+        <v>168664.35200999997</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -4969,15 +4874,15 @@
       </c>
       <c r="K29" s="68">
         <f t="shared" si="2"/>
-        <v>42234.5</v>
+        <v>0</v>
       </c>
       <c r="L29" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>21964.634999999998</v>
       </c>
       <c r="M29" s="25">
         <f t="shared" si="4"/>
-        <v>126429.85200999999</v>
+        <v>74474.811950000003</v>
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
@@ -4985,11 +4890,11 @@
       </c>
       <c r="O29" s="183">
         <f t="shared" si="6"/>
-        <v>168664.35200999997</v>
+        <v>96439.446949999998</v>
       </c>
       <c r="P29" s="7">
         <f>M29/2</f>
-        <v>63214.926004999994</v>
+        <v>37237.405975000001</v>
       </c>
       <c r="Q29" s="7">
         <f>SUM(Q15:Q28)</f>
@@ -5016,11 +4921,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="G30" s="176">
         <f>F30</f>
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -5036,15 +4941,15 @@
       </c>
       <c r="K30" s="68">
         <f t="shared" si="2"/>
-        <v>39382.300000000003</v>
+        <v>0</v>
       </c>
       <c r="L30" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20481.309000000001</v>
       </c>
       <c r="M30" s="25">
         <f t="shared" si="4"/>
-        <v>117891.73213399999</v>
+        <v>69445.344129999998</v>
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
@@ -5052,7 +4957,7 @@
       </c>
       <c r="O30" s="183">
         <f t="shared" si="6"/>
-        <v>157274.03213399998</v>
+        <v>89926.653129999992</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1">
@@ -5070,10 +4975,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>148115.79716399999</v>
+        <v>175829.73672799996</v>
       </c>
       <c r="G31" s="176">
-        <v>153655</v>
+        <f>F31</f>
+        <v>175829.73672799996</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -5085,19 +4991,19 @@
       </c>
       <c r="J31" s="24">
         <f t="shared" si="1"/>
-        <v>5539.2028360000113</v>
+        <v>0</v>
       </c>
       <c r="K31" s="68">
         <f t="shared" si="2"/>
-        <v>45415.799999999996</v>
+        <v>0</v>
       </c>
       <c r="L31" s="68">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23619.114000000001</v>
       </c>
       <c r="M31" s="25">
         <f t="shared" si="4"/>
-        <v>135953.13956399998</v>
+        <v>80084.602979999996</v>
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
@@ -5105,10 +5011,10 @@
       </c>
       <c r="O31" s="183">
         <f t="shared" si="6"/>
-        <v>175829.73672799996</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.6">
+        <v>103703.71698</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5122,32 +5028,32 @@
       </c>
       <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
-        <v>20562897.539019726</v>
+        <v>22743146.39998062</v>
       </c>
       <c r="G32" s="99">
         <f>SUM(G9:G31)</f>
-        <v>2867785.4767692201</v>
+        <v>3689620.7905269074</v>
       </c>
       <c r="H32" s="122">
         <f>SUM(H9:H31)</f>
-        <v>17895731.830543593</v>
+        <v>19304531.4759508</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>662142.07773011306</v>
+        <v>714267.66461017949</v>
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>200619.76829308967</v>
+        <v>251005.86649708962</v>
       </c>
       <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
-        <v>1097000.0000000002</v>
+        <v>0</v>
       </c>
       <c r="L32" s="90"/>
       <c r="M32" s="54">
         <f>SUM(M9:M31)</f>
-        <v>3283892.26</v>
+        <v>1934410.7000000002</v>
       </c>
       <c r="N32" s="90">
         <f>SUM(N9:N31)</f>
@@ -5155,7 +5061,7 @@
       </c>
       <c r="O32" s="54">
         <f>SUM(O9:O31)</f>
-        <v>22738146.39998062</v>
+        <v>22272713.974063884</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
@@ -5297,13 +5203,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
@@ -5351,13 +5257,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5718,7 +5624,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5740,7 +5646,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5762,7 +5668,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5784,7 +5690,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5810,7 +5716,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5832,7 +5738,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6">
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5854,7 +5760,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5876,7 +5782,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5898,7 +5804,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6">
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
